--- a/lcr_analyses/clustering/carriers/CAST/cluster_summaries_hierarchical.xlsx
+++ b/lcr_analyses/clustering/carriers/CAST/cluster_summaries_hierarchical.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4330,4 +4334,5506 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02289394783623869</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.8615384615384616</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.07179487179487179</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.7897435897435897</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6066838046272494</v>
+      </c>
+      <c r="E3" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6179129005751849</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5081395348837209</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.2161016949152543</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0614406779661017</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.602906976744186</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1639534883720931</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1199671322925226</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3008474576271186</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.05116279069767441</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1970338983050847</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2900302114803626</v>
+      </c>
+      <c r="E4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04146100691016782</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2388943731490622</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3543928923988154</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09279368213228036</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3938795656465943</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.09871668311944719</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.09871668311944719</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1204343534057256</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1135241855873643</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.06614017769002961</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2527147087857848</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1184600197433366</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0009871668311944718</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.001974333662388944</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1559723593287266</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.001974333662388944</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2458045409674235</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.2122408687068114</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.002961500493583416</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.001974333662388944</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.002961500493583416</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.01283316880552813</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6407506702412868</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05442176870748299</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6859903381642513</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1449275362318841</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1415929203539823</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.3353658536585366</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>9.329605248950895e-19</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1716417910447761</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>203</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>467</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>82</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>57</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4668192219679634</v>
+      </c>
+      <c r="E5" t="n">
+        <v>102</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.803921568627451</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.215686274509804</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.03431372549019608</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0196078431372549</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8137254901960784</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.392156862745098</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.3039215686274509</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.696078431372549</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.08823529411764709</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1372549019607844</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3674905876575544</v>
+      </c>
+      <c r="E6" t="n">
+        <v>110</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5817114483270684</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5363636363636364</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1511655011655012</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.1333333333333334</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7242424242424242</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.10439695577521</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.08787878787878788</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.202020202020202</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.006060606060606044</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.396969696969697</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.470954356846473</v>
+      </c>
+      <c r="E7" t="n">
+        <v>136</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.6262254901960784</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.4599559147685525</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1696869851729819</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.04420731707317073</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.6715328467153284</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1814285714285714</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1633109619686801</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.3391030684500393</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.009884678747940686</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1777227722772277</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.01045627376425855</v>
+      </c>
+      <c r="E8" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02289394783623869</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.8615384615384616</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.07179487179487179</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.7897435897435897</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6066838046272494</v>
+      </c>
+      <c r="E3" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6179129005751849</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5081395348837209</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.2161016949152543</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0614406779661017</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.602906976744186</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1639534883720931</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1199671322925226</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3008474576271186</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.05116279069767441</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1970338983050847</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3503875968992248</v>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.459016393442623</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5477272727272728</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.005464480874316935</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.2043795620437956</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>996</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2876348920863309</v>
+      </c>
+      <c r="E5" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04116465863453815</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2319277108433735</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.356425702811245</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.07730923694779117</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3975903614457831</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.09839357429718876</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.09939759036144578</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1184738955823293</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1154618473895582</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.06626506024096386</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2570281124497992</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1174698795180723</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.001004016064257028</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.002008032128514056</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1475903614457831</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.002008032128514056</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.2459839357429719</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.2038152610441767</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.003012048192771084</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.001004016064257028</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.003012048192771084</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.01104417670682731</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4796747967479675</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1618625277161863</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.05396825396825397</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6864934586327621</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1441285767372724</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.3392420774989333</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1700807425774048</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>198</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>455</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>82</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>57</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4668192219679634</v>
+      </c>
+      <c r="E6" t="n">
+        <v>102</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.803921568627451</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.215686274509804</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.03431372549019608</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0196078431372549</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8137254901960784</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.392156862745098</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3039215686274509</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.696078431372549</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.08823529411764709</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1372549019607844</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3674905876575544</v>
+      </c>
+      <c r="E7" t="n">
+        <v>110</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5817114483270684</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5363636363636364</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1511655011655012</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1333333333333334</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7242424242424242</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.10439695577521</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.08787878787878788</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.202020202020202</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.006060606060606044</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.396969696969697</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.470954356846473</v>
+      </c>
+      <c r="E8" t="n">
+        <v>136</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6262254901960784</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4599559147685525</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1696869851729819</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.04420731707317073</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6715328467153284</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1814285714285714</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1633109619686801</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3391030684500393</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.009884678747940686</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1777227722772277</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01045627376425855</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02289394783623869</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.8615384615384616</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.07179487179487179</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.7897435897435897</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6066838046272494</v>
+      </c>
+      <c r="E3" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6179129005751849</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5081395348837209</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.2161016949152543</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0614406779661017</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.602906976744186</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1639534883720931</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1199671322925226</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3008474576271186</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.05116279069767441</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1970338983050847</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3503875968992248</v>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.459016393442623</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5477272727272728</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.005464480874316935</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.2043795620437956</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5127992037721887</v>
+      </c>
+      <c r="E5" t="n">
+        <v>122.75</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6393601071804522</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4176773747086246</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1550047348484848</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.08956738698354971</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6807610993657506</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1632280735534803</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1745597945707997</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.3311285846438483</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-1.614586675980471e-18</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1712536255236868</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>980</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2819677384894776</v>
+      </c>
+      <c r="E6" t="n">
+        <v>92</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04183673469387755</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2336734693877551</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3459183673469388</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.07653061224489796</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3908163265306123</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.09183673469387756</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1173469387755102</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1173469387755102</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0663265306122449</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2602040816326531</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.001020408163265306</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.002040816326530612</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1346938775510204</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.002040816326530612</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.2010204081632653</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.003061224489795918</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.001020408163265306</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.003061224489795918</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.01122448979591837</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4811829002104983</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1618625277161863</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.05313205753001307</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.6869246481434848</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.147359201480698</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3403158587409519</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1699854699161217</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>195</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>446</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>63</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>82</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>57</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4668192219679634</v>
+      </c>
+      <c r="E7" t="n">
+        <v>102</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.803921568627451</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.215686274509804</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.03431372549019608</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0196078431372549</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8137254901960784</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.392156862745098</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.3039215686274509</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.696078431372549</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.08823529411764709</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1372549019607844</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3674905876575544</v>
+      </c>
+      <c r="E8" t="n">
+        <v>110</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5817114483270684</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.5363636363636364</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1511655011655012</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1333333333333334</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7242424242424242</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.10439695577521</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.08787878787878788</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.202020202020202</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.006060606060606044</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.396969696969697</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.470954356846473</v>
+      </c>
+      <c r="E9" t="n">
+        <v>136</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.6262254901960784</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.4599559147685525</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.1696869851729819</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.04420731707317073</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.6715328467153284</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1814285714285714</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1633109619686801</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.3391030684500393</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.009884678747940686</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1777227722772277</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01045627376425855</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02289394783623869</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.8615384615384616</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.07179487179487179</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.7897435897435897</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6066838046272494</v>
+      </c>
+      <c r="E3" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6179129005751849</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5081395348837209</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.2161016949152543</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0614406779661017</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.602906976744186</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1639534883720931</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1199671322925226</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3008474576271186</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.05116279069767441</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1970338983050847</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3503875968992248</v>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.459016393442623</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5477272727272728</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.005464480874316935</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.2043795620437956</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5127992037721887</v>
+      </c>
+      <c r="E5" t="n">
+        <v>122.75</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6393601071804522</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4176773747086246</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1550047348484848</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.08956738698354971</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6807610993657506</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1632280735534803</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1745597945707997</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.3311285846438483</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-1.614586675980471e-18</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1712536255236868</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>936</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2688444325977469</v>
+      </c>
+      <c r="E6" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03418803418803419</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1987179487179487</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3621794871794872</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.07478632478632478</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3760683760683761</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1036324786324786</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.08653846153846154</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.110042735042735</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1185897435897436</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.06517094017094018</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2574786324786325</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1004273504273504</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.001068376068376068</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.002136752136752137</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1356837606837607</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.001068376068376068</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2382478632478632</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1901709401709402</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.003205128205128205</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.001068376068376068</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.002136752136752137</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.009615384615384616</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6437393246616738</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4796747967479675</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1607988054814106</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.6888888888888889</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1451910408432147</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.140109647183659</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3403158587409519</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.003383940003658313</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1717104660745353</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>186</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>424</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>63</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>77</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>54</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>49</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>44</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6239156268568034</v>
+      </c>
+      <c r="E7" t="n">
+        <v>194</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2045454545454546</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9772727272727273</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7045454545454546</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.02272727272727273</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2045454545454546</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.3181818181818182</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.02272727272727273</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.4318181818181818</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.02272727272727273</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.4898785425101215</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1888216514985467</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.06244127319708714</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.6482801243795508</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1590538516998503</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1826614081215308</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.3442707835452316</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.02086047258813565</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1655183727034121</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4668192219679634</v>
+      </c>
+      <c r="E8" t="n">
+        <v>102</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.803921568627451</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.215686274509804</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.03431372549019608</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0196078431372549</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.8137254901960784</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.392156862745098</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.3039215686274509</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.696078431372549</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.08823529411764709</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1372549019607844</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3674905876575544</v>
+      </c>
+      <c r="E9" t="n">
+        <v>110</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5817114483270684</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5363636363636364</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.1511655011655012</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.1333333333333334</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7242424242424242</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.10439695577521</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.08787878787878788</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.202020202020202</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.006060606060606044</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.396969696969697</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>31</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.470954356846473</v>
+      </c>
+      <c r="E10" t="n">
+        <v>136</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.6262254901960784</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.4599559147685525</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.1696869851729819</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.04420731707317073</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.6715328467153284</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.1814285714285714</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1633109619686801</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.3391030684500393</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.009884678747940686</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1777227722772277</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01045627376425855</v>
+      </c>
+      <c r="E11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>